--- a/work/base-diaria/BASE DIÁRIA/Base Turnos_DF.xlsx
+++ b/work/base-diaria/BASE DIÁRIA/Base Turnos_DF.xlsx
@@ -105,7 +105,7 @@
     <t>Calculation Date/Time</t>
   </si>
   <si>
-    <t>09/07/2026 13:00:18</t>
+    <t>10/07/2026 13:00:46</t>
   </si>
   <si>
     <t>Reference target (IND)</t>
@@ -123,7 +123,7 @@
     <t>Datas</t>
   </si>
   <si>
-    <t>08/07/2026</t>
+    <t>09/07/2026</t>
   </si>
   <si>
     <t>Targets</t>
@@ -861,7 +861,7 @@
     <t xml:space="preserve"> 1003</t>
   </si>
   <si>
-    <t>294</t>
+    <t>293</t>
   </si>
   <si>
     <t>Remarks</t>
@@ -1287,7 +1287,7 @@
         <v>7.58</v>
       </c>
       <c r="E3" s="4">
-        <v>23.38</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1301,10 +1301,10 @@
         <v>9</v>
       </c>
       <c r="D4" s="4">
-        <v>6.40</v>
+        <v>6.15</v>
       </c>
       <c r="E4" s="4">
-        <v>33.10</v>
+        <v>35.32</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1318,10 +1318,10 @@
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <v>1.70</v>
+        <v>1.33</v>
       </c>
       <c r="E5" s="4">
-        <v>8.77</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1335,10 +1335,10 @@
         <v>11</v>
       </c>
       <c r="D6" s="4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="E6" s="4">
-        <v>5.45</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1352,10 +1352,10 @@
         <v>12</v>
       </c>
       <c r="D7" s="4">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="E7" s="4">
-        <v>1.40</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1369,10 +1369,10 @@
         <v>13</v>
       </c>
       <c r="D8" s="4">
-        <v>6.18</v>
+        <v>5.53</v>
       </c>
       <c r="E8" s="4">
-        <v>31.98</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1386,10 +1386,10 @@
         <v>14</v>
       </c>
       <c r="D9" s="4">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="E9" s="4">
-        <v>5.37</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1403,10 +1403,10 @@
         <v>15</v>
       </c>
       <c r="D10" s="4">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E10" s="4">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1420,7 +1420,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="4">
-        <v>19.34</v>
+        <v>17.41</v>
       </c>
       <c r="E11" s="4">
         <v>100.00</v>
@@ -1437,10 +1437,10 @@
         <v>9</v>
       </c>
       <c r="D12" s="4">
-        <v>9.03</v>
+        <v>10.61</v>
       </c>
       <c r="E12" s="4">
-        <v>23.53</v>
+        <v>28.97</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1454,10 +1454,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="4">
-        <v>3.71</v>
+        <v>3.49</v>
       </c>
       <c r="E13" s="4">
-        <v>9.66</v>
+        <v>9.53</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1471,10 +1471,10 @@
         <v>11</v>
       </c>
       <c r="D14" s="4">
-        <v>2.18</v>
+        <v>2.68</v>
       </c>
       <c r="E14" s="4">
-        <v>5.69</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1488,10 +1488,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="4">
-        <v>0.75</v>
+        <v>0.40</v>
       </c>
       <c r="E15" s="4">
-        <v>1.94</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1505,10 +1505,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="4">
-        <v>15.19</v>
+        <v>13.94</v>
       </c>
       <c r="E16" s="4">
-        <v>39.60</v>
+        <v>38.04</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1522,10 +1522,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="4">
-        <v>2.84</v>
+        <v>1.16</v>
       </c>
       <c r="E17" s="4">
-        <v>7.40</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1539,10 +1539,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="4">
-        <v>0.17</v>
+        <v>0.07</v>
       </c>
       <c r="E18" s="4">
-        <v>0.44</v>
+        <v>0.20</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1556,7 +1556,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="4">
-        <v>38.37</v>
+        <v>36.64</v>
       </c>
       <c r="E19" s="4">
         <v>100.00</v>
@@ -1573,10 +1573,10 @@
         <v>9</v>
       </c>
       <c r="D20" s="4">
-        <v>8.26</v>
+        <v>9.78</v>
       </c>
       <c r="E20" s="4">
-        <v>27.87</v>
+        <v>31.08</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1590,10 +1590,10 @@
         <v>10</v>
       </c>
       <c r="D21" s="4">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="E21" s="4">
-        <v>7.63</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1607,10 +1607,10 @@
         <v>11</v>
       </c>
       <c r="D22" s="4">
-        <v>2.20</v>
+        <v>2.83</v>
       </c>
       <c r="E22" s="4">
-        <v>7.44</v>
+        <v>9.00</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1624,10 +1624,10 @@
         <v>12</v>
       </c>
       <c r="D23" s="4">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="E23" s="4">
-        <v>1.29</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1641,10 +1641,10 @@
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>10.17</v>
+        <v>11.04</v>
       </c>
       <c r="E24" s="4">
-        <v>34.31</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1658,10 +1658,10 @@
         <v>14</v>
       </c>
       <c r="D25" s="4">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="E25" s="4">
-        <v>6.25</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1675,10 +1675,10 @@
         <v>15</v>
       </c>
       <c r="D26" s="4">
-        <v>0.31</v>
+        <v>0.04</v>
       </c>
       <c r="E26" s="4">
-        <v>1.06</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1692,7 +1692,7 @@
         <v>16</v>
       </c>
       <c r="D27" s="4">
-        <v>29.64</v>
+        <v>31.48</v>
       </c>
       <c r="E27" s="4">
         <v>100.00</v>
@@ -1709,10 +1709,10 @@
         <v>9</v>
       </c>
       <c r="D28" s="4">
-        <v>9.93</v>
+        <v>11.51</v>
       </c>
       <c r="E28" s="4">
-        <v>26.95</v>
+        <v>31.44</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1726,10 +1726,10 @@
         <v>10</v>
       </c>
       <c r="D29" s="4">
-        <v>3.37</v>
+        <v>2.99</v>
       </c>
       <c r="E29" s="4">
-        <v>9.14</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1743,10 +1743,10 @@
         <v>11</v>
       </c>
       <c r="D30" s="4">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="E30" s="4">
-        <v>6.30</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1760,10 +1760,10 @@
         <v>12</v>
       </c>
       <c r="D31" s="4">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="E31" s="4">
-        <v>1.65</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1777,10 +1777,10 @@
         <v>13</v>
       </c>
       <c r="D32" s="4">
-        <v>13.42</v>
+        <v>13.18</v>
       </c>
       <c r="E32" s="4">
-        <v>36.43</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1794,10 +1794,10 @@
         <v>14</v>
       </c>
       <c r="D33" s="4">
-        <v>2.32</v>
+        <v>1.46</v>
       </c>
       <c r="E33" s="4">
-        <v>6.29</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1811,10 +1811,10 @@
         <v>15</v>
       </c>
       <c r="D34" s="4">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="E34" s="4">
-        <v>0.69</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1828,7 +1828,7 @@
         <v>16</v>
       </c>
       <c r="D35" s="4">
-        <v>36.85</v>
+        <v>36.61</v>
       </c>
       <c r="E35" s="4">
         <v>100.00</v>
@@ -4461,52 +4461,52 @@
         <v>7.58</v>
       </c>
       <c r="C4" s="4">
-        <v>8.79</v>
+        <v>10.09</v>
       </c>
       <c r="D4" s="4">
-        <v>2.85</v>
+        <v>2.51</v>
       </c>
       <c r="E4" s="4">
-        <v>2.08</v>
+        <v>2.51</v>
       </c>
       <c r="F4" s="4">
-        <v>0.51</v>
+        <v>0.30</v>
       </c>
       <c r="G4" s="4">
-        <v>11.67</v>
+        <v>11.54</v>
       </c>
       <c r="H4" s="4">
-        <v>0.22</v>
+        <v>0.05</v>
       </c>
       <c r="I4" s="4">
-        <v>2.07</v>
+        <v>1.32</v>
       </c>
       <c r="J4" s="4">
-        <v>32.40</v>
+        <v>32.30</v>
       </c>
       <c r="K4" s="4">
-        <v>23.38</v>
+        <v>23.46</v>
       </c>
       <c r="L4" s="4">
-        <v>27.14</v>
+        <v>31.23</v>
       </c>
       <c r="M4" s="4">
-        <v>8.80</v>
+        <v>7.77</v>
       </c>
       <c r="N4" s="4">
-        <v>6.43</v>
+        <v>7.78</v>
       </c>
       <c r="O4" s="4">
-        <v>1.58</v>
+        <v>0.93</v>
       </c>
       <c r="P4" s="4">
-        <v>36.02</v>
+        <v>35.74</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.69</v>
+        <v>0.17</v>
       </c>
       <c r="R4" s="4">
-        <v>6.39</v>
+        <v>4.09</v>
       </c>
       <c r="S4" s="4">
         <v>100.00</v>
@@ -4517,55 +4517,55 @@
         <v>290</v>
       </c>
       <c r="B5" s="4">
-        <v>4.50</v>
+        <v>4.06</v>
       </c>
       <c r="C5" s="4">
-        <v>6.40</v>
+        <v>6.15</v>
       </c>
       <c r="D5" s="4">
-        <v>1.70</v>
+        <v>1.33</v>
       </c>
       <c r="E5" s="4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="F5" s="4">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="G5" s="4">
-        <v>6.18</v>
+        <v>5.53</v>
       </c>
       <c r="H5" s="4">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I5" s="4">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="J5" s="4">
-        <v>19.34</v>
+        <v>17.41</v>
       </c>
       <c r="K5" s="4">
-        <v>23.27</v>
+        <v>23.33</v>
       </c>
       <c r="L5" s="4">
-        <v>33.10</v>
+        <v>35.32</v>
       </c>
       <c r="M5" s="4">
-        <v>8.77</v>
+        <v>7.65</v>
       </c>
       <c r="N5" s="4">
-        <v>5.45</v>
+        <v>5.95</v>
       </c>
       <c r="O5" s="4">
-        <v>1.40</v>
+        <v>1.95</v>
       </c>
       <c r="P5" s="4">
-        <v>31.98</v>
+        <v>31.74</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="R5" s="4">
-        <v>5.37</v>
+        <v>3.79</v>
       </c>
       <c r="S5" s="4">
         <v>100.00</v>
@@ -4576,55 +4576,55 @@
         <v>291</v>
       </c>
       <c r="B6" s="4">
-        <v>9.03</v>
+        <v>8.62</v>
       </c>
       <c r="C6" s="4">
-        <v>9.03</v>
+        <v>10.61</v>
       </c>
       <c r="D6" s="4">
-        <v>3.71</v>
+        <v>3.49</v>
       </c>
       <c r="E6" s="4">
-        <v>2.18</v>
+        <v>2.68</v>
       </c>
       <c r="F6" s="4">
-        <v>0.75</v>
+        <v>0.40</v>
       </c>
       <c r="G6" s="4">
-        <v>15.19</v>
+        <v>13.94</v>
       </c>
       <c r="H6" s="4">
-        <v>0.17</v>
+        <v>0.07</v>
       </c>
       <c r="I6" s="4">
-        <v>2.84</v>
+        <v>1.16</v>
       </c>
       <c r="J6" s="4">
-        <v>38.37</v>
+        <v>36.64</v>
       </c>
       <c r="K6" s="4">
-        <v>23.53</v>
+        <v>23.54</v>
       </c>
       <c r="L6" s="4">
-        <v>23.53</v>
+        <v>28.97</v>
       </c>
       <c r="M6" s="4">
-        <v>9.66</v>
+        <v>9.53</v>
       </c>
       <c r="N6" s="4">
-        <v>5.69</v>
+        <v>7.32</v>
       </c>
       <c r="O6" s="4">
-        <v>1.94</v>
+        <v>1.09</v>
       </c>
       <c r="P6" s="4">
-        <v>39.60</v>
+        <v>38.04</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.44</v>
+        <v>0.20</v>
       </c>
       <c r="R6" s="4">
-        <v>7.40</v>
+        <v>3.16</v>
       </c>
       <c r="S6" s="4">
         <v>100.00</v>
@@ -4635,55 +4635,55 @@
         <v>292</v>
       </c>
       <c r="B7" s="4">
-        <v>6.88</v>
+        <v>7.35</v>
       </c>
       <c r="C7" s="4">
-        <v>8.26</v>
+        <v>9.78</v>
       </c>
       <c r="D7" s="4">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="E7" s="4">
-        <v>2.20</v>
+        <v>2.83</v>
       </c>
       <c r="F7" s="4">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="G7" s="4">
-        <v>10.17</v>
+        <v>11.04</v>
       </c>
       <c r="H7" s="4">
-        <v>0.31</v>
+        <v>0.04</v>
       </c>
       <c r="I7" s="4">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="J7" s="4">
-        <v>29.64</v>
+        <v>31.48</v>
       </c>
       <c r="K7" s="4">
-        <v>23.23</v>
+        <v>23.35</v>
       </c>
       <c r="L7" s="4">
-        <v>27.87</v>
+        <v>31.08</v>
       </c>
       <c r="M7" s="4">
-        <v>7.63</v>
+        <v>6.09</v>
       </c>
       <c r="N7" s="4">
-        <v>7.44</v>
+        <v>9.00</v>
       </c>
       <c r="O7" s="4">
-        <v>1.29</v>
+        <v>0.49</v>
       </c>
       <c r="P7" s="4">
-        <v>34.31</v>
+        <v>35.09</v>
       </c>
       <c r="Q7" s="4">
-        <v>1.06</v>
+        <v>0.13</v>
       </c>
       <c r="R7" s="4">
-        <v>6.25</v>
+        <v>4.88</v>
       </c>
       <c r="S7" s="4">
         <v>100.00</v>
@@ -4694,55 +4694,55 @@
         <v>293</v>
       </c>
       <c r="B8" s="4">
-        <v>8.63</v>
+        <v>8.61</v>
       </c>
       <c r="C8" s="4">
-        <v>9.93</v>
+        <v>11.51</v>
       </c>
       <c r="D8" s="4">
-        <v>3.37</v>
+        <v>2.99</v>
       </c>
       <c r="E8" s="4">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="F8" s="4">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="G8" s="4">
-        <v>13.42</v>
+        <v>13.18</v>
       </c>
       <c r="H8" s="4">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="I8" s="4">
-        <v>2.32</v>
+        <v>1.46</v>
       </c>
       <c r="J8" s="4">
-        <v>36.85</v>
+        <v>36.61</v>
       </c>
       <c r="K8" s="4">
-        <v>23.43</v>
+        <v>23.53</v>
       </c>
       <c r="L8" s="4">
-        <v>26.95</v>
+        <v>31.44</v>
       </c>
       <c r="M8" s="4">
-        <v>9.14</v>
+        <v>8.18</v>
       </c>
       <c r="N8" s="4">
-        <v>6.30</v>
+        <v>7.51</v>
       </c>
       <c r="O8" s="4">
-        <v>1.65</v>
+        <v>0.97</v>
       </c>
       <c r="P8" s="4">
-        <v>36.43</v>
+        <v>35.99</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.69</v>
+        <v>0.17</v>
       </c>
       <c r="R8" s="4">
-        <v>6.29</v>
+        <v>3.99</v>
       </c>
       <c r="S8" s="4">
         <v>100.00</v>
